--- a/諸費用明細_高松二丁目_テンプレート.xlsx
+++ b/諸費用明細_高松二丁目_テンプレート.xlsx
@@ -70,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -92,11 +92,44 @@
         <color rgb="00A0A0A0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A0A0A0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A0A0A0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A0A0A0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A0A0A0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A0A0A0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,7 +556,7 @@
           <t>盛岡市高松二丁目（アーバンキューブ＋花みずき貸家3棟）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
+      <c r="D5" s="17" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -535,7 +569,7 @@
           <t>KIKUCHIホールディングス株式会社</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
+      <c r="D6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -548,7 +582,7 @@
           <t>三浦様 ほか（売主2名）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
+      <c r="D7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -561,7 +595,7 @@
           <t>不動産管理トラステン合同会社（阿部様）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n"/>
+      <c r="D8" s="17" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -574,7 +608,7 @@
           <t>岩手銀行 花巻支店（西原様）／根抵当権 極度額60,000,000円</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
+      <c r="D9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -587,7 +621,7 @@
           <t>2026/7/31（金）午後（午前 現地確認）</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
+      <c r="D10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -600,7 +634,7 @@
           <t>2026/8/7（金）</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -613,7 +647,7 @@
           <t>2026/8/14（金）立会い無し</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
@@ -646,7 +680,7 @@
       <c r="C16" s="10" t="inlineStr"/>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>契約書で確定後入力（消費税計算用）※阿部様確認中</t>
+          <t>消費税は税込総額で通す方針（按分交渉はこちらから持ち出さない）</t>
         </is>
       </c>
     </row>
@@ -671,10 +705,12 @@
           <t>手付金</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr"/>
+      <c r="C18" s="8" t="n">
+        <v>2000000</v>
+      </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>契約時支払額。契約書ドラフトで確定後入力</t>
+          <t>各100万円×売主2系統（売主合意済み）。決済時に売買代金へ充当</t>
         </is>
       </c>
     </row>
@@ -754,12 +790,12 @@
           <t>登記費用（所有権移転＋根抵当権設定 一式）</t>
         </is>
       </c>
-      <c r="C25" s="10" t="n">
-        <v>923644</v>
+      <c r="C25" s="8" t="n">
+        <v>995000</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>小山田司法書士事務所見積ベース。岩崎先生の見積受領後に更新（土地10筆・売主複数・根抵当2件）</t>
+          <t>豊岡勝司法書士事務所 佐々木様 正式見積（報酬313,478円+実費等・手取ベース）</t>
         </is>
       </c>
     </row>
@@ -795,10 +831,12 @@
           <t>火災保険料</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr"/>
+      <c r="C28" s="8" t="n">
+        <v>190000</v>
+      </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>見積取得後入力（建物2棟＋貸家3棟分）</t>
+          <t>プランB(請求戦略型)採用見込み：アーバン10〜13万+花みずき6〜9万の中央値。大森さん見積で確定</t>
         </is>
       </c>
     </row>

--- a/諸費用明細_高松二丁目_テンプレート.xlsx
+++ b/諸費用明細_高松二丁目_テンプレート.xlsx
@@ -706,11 +706,11 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>各100万円×売主2系統（売主合意済み）。決済時に売買代金へ充当</t>
+          <t>各10万円×2契約(お借入内訳.xlsx 8/3版)。決済時に代金充当</t>
         </is>
       </c>
     </row>
@@ -721,11 +721,11 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>37000000</v>
+        <v>43200000</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>岩手銀行。根抵当極度額は60,000,000円</t>
+          <t>岩銀2本立て: ①アパート2,950万+②貸家1,370万。諸費用込み融資(変動2.75%・20年)</t>
         </is>
       </c>
     </row>
@@ -759,13 +759,12 @@
           <t>仲介手数料（税込）</t>
         </is>
       </c>
-      <c r="C23" s="11">
-        <f>ROUND((C15*0.03+60000)*1.1,0)</f>
-        <v/>
+      <c r="C23" s="8" t="n">
+        <v>1321048</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>速算式（3%+6万円）×消費税10%</t>
+          <t>実額(お借入内訳): アパート862,499+貸家458,549</t>
         </is>
       </c>
     </row>
@@ -791,11 +790,11 @@
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>995000</v>
+        <v>820000</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>豊岡勝司法書士事務所 佐々木様 正式見積（報酬313,478円+実費等・手取ベース）</t>
+          <t>お借入内訳の実額(アパート側計上)</t>
         </is>
       </c>
     </row>
@@ -805,10 +804,12 @@
           <t>印紙代（金銭消費貸借契約）</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr"/>
+      <c r="C26" s="8" t="n">
+        <v>40000</v>
+      </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>銀行契約形態により変動（電子契約なら不要）。西原様に確認</t>
+          <t>岩銀提案書: 2契約×20,000円</t>
         </is>
       </c>
     </row>
@@ -818,10 +819,12 @@
           <t>銀行事務手数料・保証料</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr"/>
+      <c r="C27" s="8" t="n">
+        <v>4278000</v>
+      </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>岩手銀行の条件確定後入力（西原様に確認）</t>
+          <t>信用保証料概算: ①292.1万+②135.7万(岩手県信用保証協会)</t>
         </is>
       </c>
     </row>
@@ -832,11 +835,11 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>190000</v>
+        <v>99900</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>プランB(請求戦略型)採用見込み：アーバン10〜13万+花みずき6〜9万の中央値。大森さん見積で確定</t>
+          <t>確定: アパート71,230+貸家28,670</t>
         </is>
       </c>
     </row>
@@ -875,11 +878,11 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>5000</v>
+        <v>60000</v>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>概算</t>
+          <t>担保調査手数料55,000(岩銀)+振込等5,000</t>
         </is>
       </c>
     </row>
